--- a/Templates/bulkImport/config/construct_NCR_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_NCR_config_sslr.xlsx
@@ -1,187 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12960"/>
+    <workbookView xWindow="204" yWindow="588" windowWidth="22716" windowHeight="8676"/>
   </bookViews>
   <sheets>
     <sheet name="ncr_raw" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>USER</author>
-    <author>User</author>
-  </authors>
-  <commentList>
-    <comment ref="E5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AH5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AL5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AN5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AR5" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Time Format:
-13:00 PM</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AS5" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="161">
   <si>
     <t>*</t>
   </si>
@@ -336,6 +169,18 @@
     <t>48</t>
   </si>
   <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
     <t>c_ref_no</t>
   </si>
   <si>
@@ -357,19 +202,7 @@
     <t>c_work_discipline</t>
   </si>
   <si>
-    <t>c_ch_1</t>
-  </si>
-  <si>
-    <t>c_ch_2</t>
-  </si>
-  <si>
-    <t>c_gridline</t>
-  </si>
-  <si>
-    <t>c_structure_element</t>
-  </si>
-  <si>
-    <t>c_others</t>
+    <t>c_location</t>
   </si>
   <si>
     <t>c_doc_reference</t>
@@ -387,12 +220,12 @@
     <t>c_originated_by</t>
   </si>
   <si>
+    <t>c_status</t>
+  </si>
+  <si>
     <t>c_coordinates</t>
   </si>
   <si>
-    <t>c_status</t>
-  </si>
-  <si>
     <t>c_action_status</t>
   </si>
   <si>
@@ -402,6 +235,24 @@
     <t>c_action_date</t>
   </si>
   <si>
+    <t>c_review_action</t>
+  </si>
+  <si>
+    <t>c_verify_remark</t>
+  </si>
+  <si>
+    <t>c_confirmed_by</t>
+  </si>
+  <si>
+    <t>c_verified_time</t>
+  </si>
+  <si>
+    <t>c_verified_date</t>
+  </si>
+  <si>
+    <t>c_resub_remark</t>
+  </si>
+  <si>
     <t>c_acknowledge</t>
   </si>
   <si>
@@ -429,9 +280,6 @@
     <t>c_further_details</t>
   </si>
   <si>
-    <t>c_proposal_attachment</t>
-  </si>
-  <si>
     <t>c_completion_date</t>
   </si>
   <si>
@@ -456,33 +304,42 @@
     <t>c_date_agreed_sec1</t>
   </si>
   <si>
-    <t>c_supporting_doc</t>
-  </si>
-  <si>
-    <t>c_supporting_remarks</t>
-  </si>
-  <si>
-    <t>c_submitted_doc_by</t>
-  </si>
-  <si>
-    <t>c_supporting_time</t>
-  </si>
-  <si>
-    <t>c_supporting_date</t>
+    <t>c_disposition_verification_pm</t>
+  </si>
+  <si>
+    <t>c_review_remark_pm</t>
+  </si>
+  <si>
+    <t>c_date_reviewed_pm</t>
+  </si>
+  <si>
+    <t>c_agreed_by_sec2</t>
+  </si>
+  <si>
+    <t>c_date_agreed_sec2</t>
+  </si>
+  <si>
+    <t>c_wir_doc_status</t>
+  </si>
+  <si>
+    <t>c_close_out_date</t>
   </si>
   <si>
     <t>c_close_verification</t>
   </si>
   <si>
-    <t>c_verification_attachment</t>
-  </si>
-  <si>
     <t>c_close_verified_by</t>
   </si>
   <si>
     <t>c_close_verified_position</t>
   </si>
   <si>
+    <t>c_close_verified_time</t>
+  </si>
+  <si>
+    <t>c_close_verified_date</t>
+  </si>
+  <si>
     <t>NCR Ref No</t>
   </si>
   <si>
@@ -504,19 +361,7 @@
     <t>Work Discipline</t>
   </si>
   <si>
-    <t>Chainage 1</t>
-  </si>
-  <si>
-    <t>Chainage 2</t>
-  </si>
-  <si>
-    <t>Gridline</t>
-  </si>
-  <si>
-    <t>Structure Element</t>
-  </si>
-  <si>
-    <t>Others</t>
+    <t>Location</t>
   </si>
   <si>
     <t>Document Ref. (Spec/Dwg./etc)</t>
@@ -534,12 +379,12 @@
     <t>Originated By</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Coordinates</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -549,6 +394,24 @@
     <t>Action Date</t>
   </si>
   <si>
+    <t>Review For Issuance Action</t>
+  </si>
+  <si>
+    <t>Review For Issuance Remark</t>
+  </si>
+  <si>
+    <t>Review For Issuance Confirmed By</t>
+  </si>
+  <si>
+    <t>Review For Issuance Time</t>
+  </si>
+  <si>
+    <t>Review For Issuance Date</t>
+  </si>
+  <si>
+    <t>Review For Issuance Resubmission Remark</t>
+  </si>
+  <si>
     <t>Acknowledge</t>
   </si>
   <si>
@@ -573,10 +436,7 @@
     <t>Disposition</t>
   </si>
   <si>
-    <t>Further Details (If Any)</t>
-  </si>
-  <si>
-    <t>Attachment(s)</t>
+    <t>Disposition Futher Details</t>
   </si>
   <si>
     <t>Target Completion Date</t>
@@ -603,16 +463,25 @@
     <t>Agreed By Date</t>
   </si>
   <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Submitted By</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Date</t>
+    <t>Is disposition acceptable? (PM)</t>
+  </si>
+  <si>
+    <t>Originator’s Remark (PM)</t>
+  </si>
+  <si>
+    <t>Disposition Reviewed Date (PM)</t>
+  </si>
+  <si>
+    <t>Agreed By Name (PM)</t>
+  </si>
+  <si>
+    <t>Agreed By Date (PM)</t>
+  </si>
+  <si>
+    <t>Document Status (WIR)</t>
+  </si>
+  <si>
+    <t>Close Out Date (WIR)</t>
   </si>
   <si>
     <t>Close Verification</t>
@@ -622,189 +491,26 @@
   </si>
   <si>
     <t>Close Verified By Position</t>
+  </si>
+  <si>
+    <t>Close Verified Time</t>
+  </si>
+  <si>
+    <t>Close Verified Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -812,193 +518,10 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1006,313 +529,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1597,58 +826,71 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AW5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BB5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88888888888889" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="1" customWidth="1"/>
-    <col min="9" max="13" width="29.6666666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.4444444444444" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.1111111111111" style="1" customWidth="1"/>
-    <col min="16" max="16" width="5.88888888888889" style="1" customWidth="1"/>
-    <col min="17" max="17" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.11111111111111" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.33333333333333" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.4444444444444" style="1" customWidth="1"/>
-    <col min="22" max="22" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="23" max="23" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="24" max="24" width="20.8888888888889" style="1" customWidth="1"/>
-    <col min="25" max="25" width="23.3333333333333" style="1" customWidth="1"/>
-    <col min="26" max="26" width="24" style="1" customWidth="1"/>
-    <col min="27" max="27" width="20" style="1" customWidth="1"/>
-    <col min="28" max="28" width="19.8888888888889" style="1" customWidth="1"/>
-    <col min="29" max="29" width="12.5555555555556" style="1" customWidth="1"/>
-    <col min="30" max="30" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="31" max="31" width="24.3333333333333" style="1" customWidth="1"/>
-    <col min="32" max="33" width="22.4444444444444" style="1" customWidth="1"/>
-    <col min="34" max="34" width="25.8888888888889" style="1" customWidth="1"/>
-    <col min="35" max="35" width="22.8888888888889" style="1" customWidth="1"/>
-    <col min="36" max="36" width="24.3333333333333" style="1" customWidth="1"/>
-    <col min="37" max="37" width="18.8888888888889" style="1" customWidth="1"/>
-    <col min="38" max="38" width="25.3333333333333" style="1" customWidth="1"/>
-    <col min="39" max="39" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="40" max="40" width="19.1111111111111" style="1" customWidth="1"/>
-    <col min="41" max="45" width="19.5555555555556" style="1" customWidth="1"/>
-    <col min="46" max="46" width="18.8888888888889" style="1" customWidth="1"/>
-    <col min="47" max="48" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="49" max="49" width="24.3333333333333" style="1" customWidth="1"/>
-    <col min="50" max="50" width="9.11111111111111" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.44140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="25.5546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="26.5546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="32" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="23.88671875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="39.6640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="14.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="20.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="23.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="24" style="1" customWidth="1"/>
+    <col min="29" max="29" width="20" style="1" customWidth="1"/>
+    <col min="30" max="30" width="19.88671875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="12.5546875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="12.6640625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="24.33203125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="22.44140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="25.88671875" style="1" customWidth="1"/>
+    <col min="36" max="36" width="22.88671875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="24.33203125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="18.88671875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="25.33203125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="17.33203125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="19.109375" style="1" customWidth="1"/>
+    <col min="42" max="42" width="29" style="1" customWidth="1"/>
+    <col min="43" max="43" width="23.6640625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="30.33203125" style="1" customWidth="1"/>
+    <col min="45" max="45" width="20.6640625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="19.5546875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="21.88671875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="19.88671875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="18.88671875" style="1" customWidth="1"/>
+    <col min="50" max="50" width="22.33203125" style="1" customWidth="1"/>
+    <col min="51" max="52" width="24.33203125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="20.6640625" style="1" customWidth="1"/>
+    <col min="54" max="54" width="9.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:53">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1673,32 +915,20 @@
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:49">
+    <row r="2" spans="1:53">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1846,8 +1076,20 @@
       <c r="AW2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="AX2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:49">
+    <row r="3" spans="1:53">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1995,310 +1237,344 @@
       <c r="AW3" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AX3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="4" spans="1:49">
+    <row r="4" spans="1:53">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AN4" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AQ4" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AR4" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AS4" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AT4" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AU4" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AV4" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BA4" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:49">
+    <row r="5" spans="1:53">
       <c r="A5" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AL5" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="AU5" s="1" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="AV5" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="AW5" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Templates/bulkImport/config/construct_NCR_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_NCR_config_sslr.xlsx
@@ -1,20 +1,187 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="588" windowWidth="22716" windowHeight="8676"/>
+    <workbookView windowWidth="27948" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="ncr_raw" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>USER</author>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AG5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AL5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AN5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AR5" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>Time Format:
+13:00 PM</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AS5" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
   <si>
     <t>*</t>
   </si>
@@ -169,18 +336,6 @@
     <t>48</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
     <t>c_ref_no</t>
   </si>
   <si>
@@ -202,7 +357,19 @@
     <t>c_work_discipline</t>
   </si>
   <si>
-    <t>c_location</t>
+    <t>c_ch_1</t>
+  </si>
+  <si>
+    <t>c_ch_2</t>
+  </si>
+  <si>
+    <t>c_gridline</t>
+  </si>
+  <si>
+    <t>c_structure_element</t>
+  </si>
+  <si>
+    <t>c_others</t>
   </si>
   <si>
     <t>c_doc_reference</t>
@@ -220,12 +387,12 @@
     <t>c_originated_by</t>
   </si>
   <si>
+    <t>c_coordinates</t>
+  </si>
+  <si>
     <t>c_status</t>
   </si>
   <si>
-    <t>c_coordinates</t>
-  </si>
-  <si>
     <t>c_action_status</t>
   </si>
   <si>
@@ -235,24 +402,6 @@
     <t>c_action_date</t>
   </si>
   <si>
-    <t>c_review_action</t>
-  </si>
-  <si>
-    <t>c_verify_remark</t>
-  </si>
-  <si>
-    <t>c_confirmed_by</t>
-  </si>
-  <si>
-    <t>c_verified_time</t>
-  </si>
-  <si>
-    <t>c_verified_date</t>
-  </si>
-  <si>
-    <t>c_resub_remark</t>
-  </si>
-  <si>
     <t>c_acknowledge</t>
   </si>
   <si>
@@ -280,6 +429,9 @@
     <t>c_further_details</t>
   </si>
   <si>
+    <t>c_proposal_attachment</t>
+  </si>
+  <si>
     <t>c_completion_date</t>
   </si>
   <si>
@@ -304,42 +456,33 @@
     <t>c_date_agreed_sec1</t>
   </si>
   <si>
-    <t>c_disposition_verification_pm</t>
-  </si>
-  <si>
-    <t>c_review_remark_pm</t>
-  </si>
-  <si>
-    <t>c_date_reviewed_pm</t>
-  </si>
-  <si>
-    <t>c_agreed_by_sec2</t>
-  </si>
-  <si>
-    <t>c_date_agreed_sec2</t>
-  </si>
-  <si>
-    <t>c_wir_doc_status</t>
-  </si>
-  <si>
-    <t>c_close_out_date</t>
+    <t>c_supporting_doc</t>
+  </si>
+  <si>
+    <t>c_supporting_remarks</t>
+  </si>
+  <si>
+    <t>c_submitted_doc_by</t>
+  </si>
+  <si>
+    <t>c_supporting_time</t>
+  </si>
+  <si>
+    <t>c_supporting_date</t>
   </si>
   <si>
     <t>c_close_verification</t>
   </si>
   <si>
+    <t>c_verification_attachment</t>
+  </si>
+  <si>
     <t>c_close_verified_by</t>
   </si>
   <si>
     <t>c_close_verified_position</t>
   </si>
   <si>
-    <t>c_close_verified_time</t>
-  </si>
-  <si>
-    <t>c_close_verified_date</t>
-  </si>
-  <si>
     <t>NCR Ref No</t>
   </si>
   <si>
@@ -361,7 +504,19 @@
     <t>Work Discipline</t>
   </si>
   <si>
-    <t>Location</t>
+    <t>Chainage 1</t>
+  </si>
+  <si>
+    <t>Chainage 2</t>
+  </si>
+  <si>
+    <t>Gridline</t>
+  </si>
+  <si>
+    <t>Structure Element</t>
+  </si>
+  <si>
+    <t>Others</t>
   </si>
   <si>
     <t>Document Ref. (Spec/Dwg./etc)</t>
@@ -379,12 +534,12 @@
     <t>Originated By</t>
   </si>
   <si>
+    <t>Coordinates</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Coordinates</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -394,24 +549,6 @@
     <t>Action Date</t>
   </si>
   <si>
-    <t>Review For Issuance Action</t>
-  </si>
-  <si>
-    <t>Review For Issuance Remark</t>
-  </si>
-  <si>
-    <t>Review For Issuance Confirmed By</t>
-  </si>
-  <si>
-    <t>Review For Issuance Time</t>
-  </si>
-  <si>
-    <t>Review For Issuance Date</t>
-  </si>
-  <si>
-    <t>Review For Issuance Resubmission Remark</t>
-  </si>
-  <si>
     <t>Acknowledge</t>
   </si>
   <si>
@@ -436,7 +573,10 @@
     <t>Disposition</t>
   </si>
   <si>
-    <t>Disposition Futher Details</t>
+    <t>Further Details (If Any)</t>
+  </si>
+  <si>
+    <t>Attachment(s)</t>
   </si>
   <si>
     <t>Target Completion Date</t>
@@ -463,25 +603,16 @@
     <t>Agreed By Date</t>
   </si>
   <si>
-    <t>Is disposition acceptable? (PM)</t>
-  </si>
-  <si>
-    <t>Originator’s Remark (PM)</t>
-  </si>
-  <si>
-    <t>Disposition Reviewed Date (PM)</t>
-  </si>
-  <si>
-    <t>Agreed By Name (PM)</t>
-  </si>
-  <si>
-    <t>Agreed By Date (PM)</t>
-  </si>
-  <si>
-    <t>Document Status (WIR)</t>
-  </si>
-  <si>
-    <t>Close Out Date (WIR)</t>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Submitted By</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
   <si>
     <t>Close Verification</t>
@@ -491,26 +622,189 @@
   </si>
   <si>
     <t>Close Verified By Position</t>
-  </si>
-  <si>
-    <t>Close Verified Time</t>
-  </si>
-  <si>
-    <t>Close Verified Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,10 +812,193 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -529,19 +1006,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -826,71 +1597,58 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BB5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AW5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1111111111111" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88888888888889" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6666666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.33203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.44140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.44140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="25.5546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="26.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32" style="1" customWidth="1"/>
-    <col min="22" max="22" width="24.109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="23.88671875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="39.6640625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="20.88671875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="23.33203125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="24" style="1" customWidth="1"/>
-    <col min="29" max="29" width="20" style="1" customWidth="1"/>
-    <col min="30" max="30" width="19.88671875" style="1" customWidth="1"/>
-    <col min="31" max="31" width="12.5546875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.6640625" style="1" customWidth="1"/>
-    <col min="33" max="33" width="24.33203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="22.44140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="25.88671875" style="1" customWidth="1"/>
-    <col min="36" max="36" width="22.88671875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="24.33203125" style="1" customWidth="1"/>
-    <col min="38" max="38" width="18.88671875" style="1" customWidth="1"/>
-    <col min="39" max="39" width="25.33203125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="17.33203125" style="1" customWidth="1"/>
-    <col min="41" max="41" width="19.109375" style="1" customWidth="1"/>
-    <col min="42" max="42" width="29" style="1" customWidth="1"/>
-    <col min="43" max="43" width="23.6640625" style="1" customWidth="1"/>
-    <col min="44" max="44" width="30.33203125" style="1" customWidth="1"/>
-    <col min="45" max="45" width="20.6640625" style="1" customWidth="1"/>
-    <col min="46" max="46" width="19.5546875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="21.88671875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="19.88671875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="18.88671875" style="1" customWidth="1"/>
-    <col min="50" max="50" width="22.33203125" style="1" customWidth="1"/>
-    <col min="51" max="52" width="24.33203125" style="1" customWidth="1"/>
-    <col min="53" max="53" width="20.6640625" style="1" customWidth="1"/>
-    <col min="54" max="54" width="9.109375" style="1" customWidth="1"/>
+    <col min="9" max="13" width="29.6666666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.4444444444444" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1111111111111" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.88888888888889" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.4444444444444" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.11111111111111" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33333333333333" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.4444444444444" style="1" customWidth="1"/>
+    <col min="22" max="22" width="13.4444444444444" style="1" customWidth="1"/>
+    <col min="23" max="23" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="24" max="24" width="20.8888888888889" style="1" customWidth="1"/>
+    <col min="25" max="25" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="26" max="26" width="24" style="1" customWidth="1"/>
+    <col min="27" max="27" width="20" style="1" customWidth="1"/>
+    <col min="28" max="28" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="29" max="29" width="12.5555555555556" style="1" customWidth="1"/>
+    <col min="30" max="30" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="31" max="31" width="24.3333333333333" style="1" customWidth="1"/>
+    <col min="32" max="33" width="22.4444444444444" style="1" customWidth="1"/>
+    <col min="34" max="34" width="25.8888888888889" style="1" customWidth="1"/>
+    <col min="35" max="35" width="22.8888888888889" style="1" customWidth="1"/>
+    <col min="36" max="36" width="24.3333333333333" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.8888888888889" style="1" customWidth="1"/>
+    <col min="38" max="38" width="25.3333333333333" style="1" customWidth="1"/>
+    <col min="39" max="39" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="40" max="40" width="19.1111111111111" style="1" customWidth="1"/>
+    <col min="41" max="45" width="19.5555555555556" style="1" customWidth="1"/>
+    <col min="46" max="46" width="18.8888888888889" style="1" customWidth="1"/>
+    <col min="47" max="48" width="22.3333333333333" style="1" customWidth="1"/>
+    <col min="49" max="49" width="24.3333333333333" style="1" customWidth="1"/>
+    <col min="50" max="50" width="9.11111111111111" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,20 +1673,32 @@
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:49">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1076,20 +1846,8 @@
       <c r="AW2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AX2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:49">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1237,344 +1995,310 @@
       <c r="AW3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AX3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:49">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AY3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AZ3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BA3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="4" spans="1:53">
-      <c r="A4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AS4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AT4" s="1" t="s">
+    <row r="5" spans="1:49">
+      <c r="A5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AU4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AV4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AW4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AX4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AY4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AZ4" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="BA4" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="1:53">
-      <c r="A5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="AB5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="AC5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="AD5" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="AE5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="AF5" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="AG5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="AH5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AI5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AB5" s="1" t="s">
+      <c r="AJ5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AK5" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AL5" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AM5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AN5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AG5" s="1" t="s">
+      <c r="AO5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AH5" s="1" t="s">
+      <c r="AQ5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AI5" s="1" t="s">
+      <c r="AR5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AJ5" s="1" t="s">
+      <c r="AS5" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="AK5" s="1" t="s">
+      <c r="AT5" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AL5" s="1" t="s">
+      <c r="AU5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AV5" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="AM5" s="1" t="s">
+      <c r="AW5" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AR5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AS5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AT5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AU5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AW5" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AX5" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AY5" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AZ5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="BA5" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>